--- a/data/trans_camb/IQ26A_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IQ26A_R2-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,09</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,09</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>3,59</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,22</t>
+          <t>-2,45; 7,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 2,34</t>
+          <t>-4,78; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 26,59</t>
+          <t>-6,0; 16,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,03</t>
+          <t>-6,65; 2,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,89</t>
+          <t>-6,85; 2,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 12,52</t>
+          <t>-4,09; 28,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,47</t>
+          <t>-3,13; 3,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,15</t>
+          <t>-4,54; 1,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 15,02</t>
+          <t>-3,31; 16,29</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-3,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-1,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-35,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-35,84%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,59%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-29,35%</t>
+          <t>111,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 96,69</t>
+          <t>-40,93; 289,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 86,01</t>
+          <t>-71,46; 168,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,46; 778,5</t>
+          <t>-100,0; 660,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 298,59</t>
+          <t>-78,91; 105,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 161,78</t>
+          <t>-81,63; 121,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 696,2</t>
+          <t>-73,74; 733,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 99,0</t>
+          <t>-44,66; 99,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 62,49</t>
+          <t>-64,04; 54,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 396,75</t>
+          <t>-57,75; 430,19</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,07</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,95</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,22</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>18,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>13,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,36</t>
+          <t>-7,31; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,35</t>
+          <t>-2,5; 7,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 40,09</t>
+          <t>-0,05; 23,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 1,82</t>
+          <t>-6,51; 1,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 7,24</t>
+          <t>0,85; 10,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 19,15</t>
+          <t>7,47; 31,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,37</t>
+          <t>-5,66; 0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,45</t>
+          <t>-0,05; 6,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 24,47</t>
+          <t>5,75; 22,37</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-23,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71,74%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-27,87%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>56,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>241,45%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-23,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>197,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>129,12%</t>
+          <t>121,66%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 19,27</t>
+          <t>-49,84; 19,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 138,17</t>
+          <t>-17,85; 66,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99,71; 551,16</t>
+          <t>-5,18; 218,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 17,72</t>
+          <t>-57,6; 20,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 72,19</t>
+          <t>6,65; 143,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 174,52</t>
+          <t>66,83; 412,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 4,04</t>
+          <t>-45,45; 3,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 80,48</t>
+          <t>-0,46; 75,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,72; 239,1</t>
+          <t>44,6; 218,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,47</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,12</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,31</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,47</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>7,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 7,0</t>
+          <t>-5,51; 5,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 8,3</t>
+          <t>-0,27; 11,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 19,3</t>
+          <t>2,01; 24,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,8</t>
+          <t>-5,97; 7,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 11,48</t>
+          <t>-4,43; 8,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 26,3</t>
+          <t>-3,33; 20,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 4,97</t>
+          <t>-3,67; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 8,03</t>
+          <t>-0,51; 8,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 19,22</t>
+          <t>2,38; 18,67</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116,88%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>4,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>17,37%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>124,49%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 71,78</t>
+          <t>-41,28; 85,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 87,47</t>
+          <t>-4,36; 155,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 183,53</t>
+          <t>9,7; 279,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 79,52</t>
+          <t>-37,1; 74,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 154,46</t>
+          <t>-26,75; 88,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,22; 354,49</t>
+          <t>-26,25; 195,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 54,07</t>
+          <t>-26,63; 53,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 84,03</t>
+          <t>-3,51; 87,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,65; 187,88</t>
+          <t>18,26; 183,66</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,97</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-5,69</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,97</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 1,51</t>
+          <t>-5,85; 5,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 5,14</t>
+          <t>-2,88; 10,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 15,73</t>
+          <t>-8,24; 9,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 6,2</t>
+          <t>-12,76; 0,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 10,19</t>
+          <t>-8,75; 5,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 7,74</t>
+          <t>-7,21; 14,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,44</t>
+          <t>-8,13; 1,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,75</t>
+          <t>-4,35; 5,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 7,02</t>
+          <t>-6,22; 7,47</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-1,67%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-1,26%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-24,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-9,25%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,67%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-8,79%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 8,15</t>
+          <t>-30,81; 41,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 25,54</t>
+          <t>-15,67; 70,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 76,47</t>
+          <t>-45,13; 65,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 45,98</t>
+          <t>-47,26; 4,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 69,1</t>
+          <t>-33,19; 25,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 55,42</t>
+          <t>-28,37; 70,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 7,85</t>
+          <t>-36,05; 8,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 26,5</t>
+          <t>-20,44; 29,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 38,18</t>
+          <t>-28,56; 40,69</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,41</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10,59</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,15</t>
+          <t>-3,91; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,97</t>
+          <t>-0,53; 5,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 18,08</t>
+          <t>1,58; 12,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,92</t>
+          <t>-6,06; -0,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,57</t>
+          <t>-1,95; 4,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 12,5</t>
+          <t>4,06; 17,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,14</t>
+          <t>-3,97; 0,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,86</t>
+          <t>-0,36; 4,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,27</t>
+          <t>3,96; 12,6</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-8,56%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>54,43%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,98%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>77,67%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-8,56%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -0,51</t>
+          <t>-30,23; 15,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 32,64</t>
+          <t>-4,16; 49,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34,29; 142,83</t>
+          <t>11,39; 113,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 19,13</t>
+          <t>-40,28; -0,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 51,08</t>
+          <t>-12,82; 34,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,11; 109,75</t>
+          <t>27,11; 137,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -1,21</t>
+          <t>-28,75; -0,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 33,23</t>
+          <t>-2,56; 33,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29,2; 101,06</t>
+          <t>29,18; 103,04</t>
         </is>
       </c>
     </row>
